--- a/data.xlsx
+++ b/data.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,6 +693,91 @@
         </is>
       </c>
       <c r="C16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>可孚医疗</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>开始申购</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>可孚医疗</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>截止申购</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>可孚医疗</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>公布中签</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>可孚医疗</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>暗盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>可孚医疗</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
@@ -10107,32 +10192,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>123061</t>
+          <t>127066</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>航新转债</t>
+          <t>科利转债</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58.13</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>133.17</t>
+          <t>148.55</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.28年</t>
+          <t>2.23年</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -10149,32 +10234,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>127041</t>
+          <t>123142</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>弘亚转债</t>
+          <t>申昊转债</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>57.98</t>
+          <t>58.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>122.01</t>
+          <t>124.47</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.25年</t>
+          <t>1.92年</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -10191,32 +10276,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>128125</t>
+          <t>123112</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>华阳转债</t>
+          <t>万讯转债</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>58.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>119.84</t>
+          <t>137.52</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.30年</t>
+          <t>0.98年</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -10233,32 +10318,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>123138</t>
+          <t>118027</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>丝路转债</t>
+          <t>宏图转债</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>57.87</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>130.94</t>
+          <t>96.65</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.90年</t>
+          <t>2.62年</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -10275,32 +10360,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>123113</t>
+          <t>123144</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>仙乐转债</t>
+          <t>裕兴转债</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>57.70</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>121.85</t>
+          <t>127.60</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.02年</t>
+          <t>1.99年</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -10317,32 +10402,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>123080</t>
+          <t>113653</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>海波转债</t>
+          <t>永22转债</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>56.76</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>140.72</t>
+          <t>109.83</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.65年</t>
+          <t>2.28年</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -10359,32 +10444,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>123112</t>
+          <t>123171</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>万讯转债</t>
+          <t>共同转债</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56.75</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>136.71</t>
+          <t>130.87</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.99年</t>
+          <t>2.62年</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -10401,32 +10486,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>123109</t>
+          <t>127089</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>昌红转债</t>
+          <t>晶澳转债</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56.75</t>
+          <t>56.89</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>129.02</t>
+          <t>127.59</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.98年</t>
+          <t>3.25年</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -10443,32 +10528,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>123090</t>
+          <t>118032</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>三诺转债</t>
+          <t>建龙转债</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>56.58</t>
+          <t>56.71</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>116.61</t>
+          <t>129.35</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>148.5%</t>
+          <t>158.7%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.70年</t>
+          <t>2.89年</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -10485,32 +10570,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>123171</t>
+          <t>127084</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>共同转债</t>
+          <t>柳工转2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>56.61</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>128.98</t>
+          <t>144.81</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.64年</t>
+          <t>2.95年</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10583,37 +10668,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>113052</t>
+          <t>123061</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>兴业转债</t>
+          <t>航新转债</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58.35</t>
+          <t>58.13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>120.42</t>
+          <t>133.17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.73年</t>
+          <t>0.28年</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>-3.92%</t>
         </is>
       </c>
     </row>
@@ -10635,27 +10720,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>57.73</t>
+          <t>57.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>120.70</t>
+          <t>122.01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.27年</t>
+          <t>0.25年</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
@@ -10667,37 +10752,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>113043</t>
+          <t>128125</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>财通转债</t>
+          <t>华阳转债</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.43</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>122.23</t>
+          <t>119.84</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.69年</t>
+          <t>0.30年</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>+2.21%</t>
+          <t>-0.41%</t>
         </is>
       </c>
     </row>
@@ -10709,37 +10794,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>113042</t>
+          <t>123138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上银转债</t>
+          <t>丝路转债</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>124.00</t>
+          <t>130.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.81年</t>
+          <t>1.90年</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.64%</t>
         </is>
       </c>
     </row>
@@ -10751,37 +10836,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>123109</t>
+          <t>123113</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>昌红转债</t>
+          <t>仙乐转债</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>125.33</t>
+          <t>121.85</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>125.4%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.99年</t>
+          <t>1.02年</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>+3.07%</t>
+          <t>-2.31%</t>
         </is>
       </c>
     </row>
@@ -10793,37 +10878,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113062</t>
+          <t>123080</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>常银转债</t>
+          <t>海波转债</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>56.64</t>
+          <t>56.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>129.61</t>
+          <t>140.72</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.45年</t>
+          <t>0.65年</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>+0.91%</t>
+          <t>-0.21%</t>
         </is>
       </c>
     </row>
@@ -10835,37 +10920,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>127103</t>
+          <t>123112</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>东南转债</t>
+          <t>万讯转债</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56.46</t>
+          <t>56.75</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>141.30</t>
+          <t>136.71</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.76年</t>
+          <t>0.99年</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.34%</t>
         </is>
       </c>
     </row>
@@ -10877,37 +10962,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>128128</t>
+          <t>123109</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>齐翔转2</t>
+          <t>昌红转债</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56.44</t>
+          <t>56.75</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>131.03</t>
+          <t>129.02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.38年</t>
+          <t>0.98年</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>-0.71%</t>
         </is>
       </c>
     </row>
@@ -10919,37 +11004,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>127084</t>
+          <t>123090</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>柳工转2</t>
+          <t>三诺转债</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>56.30</t>
+          <t>56.58</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>145.38</t>
+          <t>116.61</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>148.5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.98年</t>
+          <t>0.70年</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.57%</t>
+          <t>-1.29%</t>
         </is>
       </c>
     </row>
@@ -10961,37 +11046,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>110081</t>
+          <t>123171</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>闻泰转债</t>
+          <t>共同转债</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>56.06</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>111.24</t>
+          <t>128.98</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.32年</t>
+          <t>2.64年</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.64%</t>
+          <t>+1.52%</t>
         </is>
       </c>
     </row>
@@ -11064,17 +11149,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-12.68%</t>
+          <t>-12.73%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.42%</t>
+          <t>22.38%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.633</t>
+          <t>-0.636</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -11089,7 +11174,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
@@ -11106,17 +11191,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-13.47%</t>
+          <t>-13.56%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.97%</t>
+          <t>21.94%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.681</t>
+          <t>-0.686</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -11131,7 +11216,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -11148,17 +11233,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.74%</t>
+          <t>15.72%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-0.029</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -11173,7 +11258,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.2%</t>
         </is>
       </c>
     </row>
@@ -11190,17 +11275,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.70%</t>
+          <t>8.59%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.23%</t>
+          <t>17.21%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.412</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -11215,7 +11300,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -11232,17 +11317,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14.12%</t>
+          <t>14.10%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.091</t>
+          <t>-0.085</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -11257,7 +11342,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -11274,17 +11359,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.77%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.66%</t>
+          <t>14.64%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.285</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -11299,7 +11384,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -11316,12 +11401,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.07%</t>
+          <t>12.06%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -11341,7 +11426,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -11358,17 +11443,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11.02%</t>
+          <t>11.04%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.42%</t>
+          <t>13.40%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>0.712</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -11383,7 +11468,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
@@ -11400,17 +11485,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.16%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.87%</t>
+          <t>11.85%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -11425,7 +11510,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
     </row>
@@ -11442,17 +11527,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10.22%</t>
+          <t>10.23%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.80%</t>
+          <t>12.78%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>0.683</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -11467,7 +11552,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -11484,17 +11569,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.68%</t>
+          <t>9.61%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.59%</t>
+          <t>11.58%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.700</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -11509,7 +11594,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -11526,17 +11611,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14.57%</t>
+          <t>14.56%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.51%</t>
+          <t>12.49%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1.046</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -11551,7 +11636,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
     </row>
@@ -11568,17 +11653,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13.59%</t>
+          <t>13.39%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11.74%</t>
+          <t>11.73%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.030</t>
+          <t>1.014</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -11593,7 +11678,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.3%</t>
         </is>
       </c>
     </row>
@@ -11610,17 +11695,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18.74%</t>
+          <t>18.54%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12.98%</t>
+          <t>12.97%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.314</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11635,7 +11720,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -11652,17 +11737,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12.01%</t>
+          <t>11.88%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10.77%</t>
+          <t>10.76%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.976</t>
+          <t>0.964</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11677,7 +11762,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -11694,17 +11779,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20.36%</t>
+          <t>20.17%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.25%</t>
+          <t>12.24%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.539</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11719,7 +11804,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -11736,17 +11821,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14.45%</t>
+          <t>14.27%</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.08%</t>
+          <t>12.07%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.072</t>
+          <t>1.058</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11761,7 +11846,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.2%</t>
         </is>
       </c>
     </row>
@@ -11778,17 +11863,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.91%</t>
+          <t>19.71%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.37%</t>
+          <t>12.36%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11803,7 +11888,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.1%</t>
         </is>
       </c>
     </row>
@@ -11820,17 +11905,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18.90%</t>
+          <t>18.81%</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11.32%</t>
+          <t>11.30%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.532</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11845,7 +11930,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.5%</t>
         </is>
       </c>
     </row>
@@ -11862,17 +11947,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>25.63%</t>
+          <t>25.49%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12.84%</t>
+          <t>12.83%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>1.870</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11887,7 +11972,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.6%</t>
         </is>
       </c>
     </row>
@@ -11904,12 +11989,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>31.59%</t>
+          <t>31.54%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19.45%</t>
+          <t>19.42%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -11929,7 +12014,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.1%</t>
         </is>
       </c>
     </row>
@@ -11946,12 +12031,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>39.10%</t>
+          <t>39.05%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17.90%</t>
+          <t>17.87%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11971,7 +12056,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -11988,17 +12073,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>25.73%</t>
+          <t>25.50%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.90%</t>
+          <t>13.89%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>1.728</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -12013,7 +12098,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.6%</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,142 @@
       <c r="C21" t="inlineStr">
         <is>
           <t>上市</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>乐动机器人</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>开始申购</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>乐动机器人</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>截止申购</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>乐动机器人</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>公布中签</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>乐动机器人</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>暗盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>乐动机器人</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>剂泰</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>开始申购</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>剂泰</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>截止申购</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>剂泰</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>公布中签</t>
         </is>
       </c>
     </row>
@@ -2480,6 +2616,9 @@
           <t>海昌智能</t>
         </is>
       </c>
+      <c r="C49" s="1" t="n">
+        <v>46139</v>
+      </c>
       <c r="D49" t="n">
         <v>20.93</v>
       </c>
@@ -2488,6 +2627,15 @@
       </c>
       <c r="F49" t="n">
         <v>910</v>
+      </c>
+      <c r="G49" t="n">
+        <v>93.98</v>
+      </c>
+      <c r="H49" t="n">
+        <v>7.478703239583334</v>
+      </c>
+      <c r="I49" t="n">
+        <v>7.889621000000001</v>
       </c>
       <c r="J49" s="1" t="n">
         <v>46127</v>
@@ -10202,22 +10350,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>148.55</t>
+          <t>146.40</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.23年</t>
+          <t>2.21年</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -10234,32 +10382,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>123142</t>
+          <t>110092</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>申昊转债</t>
+          <t>三房转债</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>58.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>124.47</t>
+          <t>104.47</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.92年</t>
+          <t>2.71年</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -10276,32 +10424,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>123112</t>
+          <t>128142</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>万讯转债</t>
+          <t>新乳转债</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>58.12</t>
+          <t>57.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>137.52</t>
+          <t>131.56</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.98年</t>
+          <t>0.65年</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -10318,32 +10466,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>118027</t>
+          <t>123065</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>宏图转债</t>
+          <t>宝莱转债</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.87</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>96.65</t>
+          <t>125.86</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.62年</t>
+          <t>0.36年</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -10360,32 +10508,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>123144</t>
+          <t>113043</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>裕兴转债</t>
+          <t>财通转债</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.70</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>127.60</t>
+          <t>127.57</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.99年</t>
+          <t>0.63年</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -10402,32 +10550,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113653</t>
+          <t>113605</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>永22转债</t>
+          <t>大参转债</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>57.37</t>
+          <t>57.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>109.83</t>
+          <t>123.51</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.28年</t>
+          <t>0.50年</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -10444,32 +10592,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>123171</t>
+          <t>123198</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>共同转债</t>
+          <t>金埔转债</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>130.87</t>
+          <t>140.24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.62年</t>
+          <t>3.13年</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -10486,32 +10634,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>127089</t>
+          <t>113627</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>晶澳转债</t>
+          <t>太平转债</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56.89</t>
+          <t>56.72</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>127.59</t>
+          <t>122.83</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.25年</t>
+          <t>1.22年</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -10528,12 +10676,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>118032</t>
+          <t>127084</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>建龙转债</t>
+          <t>柳工转2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10543,17 +10691,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>129.35</t>
+          <t>141.95</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>158.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.89年</t>
+          <t>2.93年</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -10570,32 +10718,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>127084</t>
+          <t>110085</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>柳工转2</t>
+          <t>通22转债</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>56.61</t>
+          <t>56.69</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>144.81</t>
+          <t>123.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>138.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.95年</t>
+          <t>1.84年</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10668,37 +10816,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>123061</t>
+          <t>127066</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>航新转债</t>
+          <t>科利转债</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58.13</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>133.17</t>
+          <t>148.55</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.28年</t>
+          <t>2.23年</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-3.92%</t>
+          <t>-3.49%</t>
         </is>
       </c>
     </row>
@@ -10710,37 +10858,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>127041</t>
+          <t>123142</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>弘亚转债</t>
+          <t>申昊转债</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>57.98</t>
+          <t>58.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>122.01</t>
+          <t>124.47</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.25年</t>
+          <t>1.92年</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+3.82%</t>
         </is>
       </c>
     </row>
@@ -10752,37 +10900,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>128125</t>
+          <t>123112</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>华阳转债</t>
+          <t>万讯转债</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>58.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>119.84</t>
+          <t>137.52</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.30年</t>
+          <t>0.98年</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.47%</t>
         </is>
       </c>
     </row>
@@ -10794,37 +10942,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>123138</t>
+          <t>118027</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>丝路转债</t>
+          <t>宏图转债</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>57.87</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>130.94</t>
+          <t>96.65</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.90年</t>
+          <t>2.62年</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>-4.71%</t>
         </is>
       </c>
     </row>
@@ -10836,37 +10984,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>123113</t>
+          <t>123144</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>仙乐转债</t>
+          <t>裕兴转债</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>57.70</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>121.85</t>
+          <t>127.60</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.02年</t>
+          <t>1.99年</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>+1.05%</t>
         </is>
       </c>
     </row>
@@ -10878,37 +11026,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>123080</t>
+          <t>113653</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>海波转债</t>
+          <t>永22转债</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>56.76</t>
+          <t>57.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>140.72</t>
+          <t>109.83</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.65年</t>
+          <t>2.28年</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10920,37 +11068,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>123112</t>
+          <t>123171</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>万讯转债</t>
+          <t>共同转债</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56.75</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>136.71</t>
+          <t>130.87</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.99年</t>
+          <t>2.62年</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>+5.00%</t>
         </is>
       </c>
     </row>
@@ -10962,37 +11110,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>123109</t>
+          <t>127089</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>昌红转债</t>
+          <t>晶澳转债</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56.75</t>
+          <t>56.89</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>129.02</t>
+          <t>127.59</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.98年</t>
+          <t>3.25年</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-0.95%</t>
         </is>
       </c>
     </row>
@@ -11004,37 +11152,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>123090</t>
+          <t>118032</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>三诺转债</t>
+          <t>建龙转债</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>56.58</t>
+          <t>56.71</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>116.61</t>
+          <t>129.35</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>148.5%</t>
+          <t>158.7%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.70年</t>
+          <t>2.89年</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.23%</t>
         </is>
       </c>
     </row>
@@ -11046,37 +11194,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>123171</t>
+          <t>127084</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>共同转债</t>
+          <t>柳工转2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>56.61</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>128.98</t>
+          <t>144.81</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.64年</t>
+          <t>2.95年</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>-3.28%</t>
         </is>
       </c>
     </row>
@@ -11149,17 +11297,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-12.73%</t>
+          <t>-12.16%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.38%</t>
+          <t>22.39%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.636</t>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -11174,7 +11322,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.6%</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11339,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-13.56%</t>
+          <t>-13.10%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11201,7 +11349,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.686</t>
+          <t>-0.666</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -11216,7 +11364,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
     </row>
@@ -11233,17 +11381,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.72%</t>
+          <t>15.70%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.029</t>
+          <t>-0.017</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -11258,7 +11406,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>49.4%</t>
         </is>
       </c>
     </row>
@@ -11275,17 +11423,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.59%</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.21%</t>
+          <t>17.18%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -11300,7 +11448,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -11317,17 +11465,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14.10%</t>
+          <t>14.08%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.085</t>
+          <t>-0.079</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -11342,7 +11490,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11512,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.64%</t>
+          <t>14.61%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -11384,7 +11532,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -11401,17 +11549,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.06%</t>
+          <t>12.04%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>0.449</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -11426,7 +11574,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -11443,17 +11591,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11.04%</t>
+          <t>11.00%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.40%</t>
+          <t>13.38%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>0.710</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -11468,7 +11616,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -11485,17 +11633,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.85%</t>
+          <t>11.84%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.216</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -11510,7 +11658,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
     </row>
@@ -11527,17 +11675,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10.23%</t>
+          <t>10.22%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.78%</t>
+          <t>12.76%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>0.684</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -11552,7 +11700,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -11569,17 +11717,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.61%</t>
+          <t>9.55%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.58%</t>
+          <t>11.56%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.697</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -11594,7 +11742,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
     </row>
@@ -11611,17 +11759,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14.56%</t>
+          <t>14.50%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.49%</t>
+          <t>12.47%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.046</t>
+          <t>1.042</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -11636,7 +11784,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.0%</t>
         </is>
       </c>
     </row>
@@ -11653,12 +11801,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13.39%</t>
+          <t>13.38%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11.73%</t>
+          <t>11.71%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -11678,7 +11826,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
     </row>
@@ -11695,17 +11843,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18.54%</t>
+          <t>18.59%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12.97%</t>
+          <t>12.95%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.314</t>
+          <t>1.320</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11720,7 +11868,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.4%</t>
         </is>
       </c>
     </row>
@@ -11737,17 +11885,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11.88%</t>
+          <t>11.84%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10.76%</t>
+          <t>10.75%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.964</t>
+          <t>0.963</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11762,7 +11910,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -11779,17 +11927,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20.17%</t>
+          <t>20.27%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.24%</t>
+          <t>12.22%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11804,7 +11952,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
     </row>
@@ -11821,17 +11969,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14.27%</t>
+          <t>14.29%</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.07%</t>
+          <t>12.05%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1.061</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11846,7 +11994,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -11863,12 +12011,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.71%</t>
+          <t>19.67%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.36%</t>
+          <t>12.34%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -11888,7 +12036,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.2%</t>
         </is>
       </c>
     </row>
@@ -11905,7 +12053,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18.81%</t>
+          <t>18.57%</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -11915,7 +12063,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11930,7 +12078,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -11947,17 +12095,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>25.49%</t>
+          <t>25.27%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12.83%</t>
+          <t>12.82%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.870</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11972,7 +12120,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.4%</t>
         </is>
       </c>
     </row>
@@ -11989,17 +12137,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>31.54%</t>
+          <t>30.74%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19.42%</t>
+          <t>19.49%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -12014,7 +12162,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.9%</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12179,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>39.05%</t>
+          <t>38.38%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17.87%</t>
+          <t>17.92%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.101</t>
+          <t>2.058</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -12056,7 +12204,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
     </row>
@@ -12073,17 +12221,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>25.50%</t>
+          <t>25.06%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.89%</t>
+          <t>13.91%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.728</t>
+          <t>1.694</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -12098,7 +12246,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.4%</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -10340,32 +10340,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>127066</t>
+          <t>127084</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>科利转债</t>
+          <t>柳工转2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>146.40</t>
+          <t>141.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.21年</t>
+          <t>2.93年</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -10382,32 +10382,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110092</t>
+          <t>113661</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>三房转债</t>
+          <t>福22转债</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>58.91</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>141.37</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.71年</t>
+          <t>2.58年</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -10424,32 +10424,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>128142</t>
+          <t>128125</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新乳转债</t>
+          <t>华阳转债</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.55</t>
+          <t>58.19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>131.56</t>
+          <t>117.24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.65年</t>
+          <t>0.27年</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -10466,32 +10466,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>123065</t>
+          <t>123198</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>宝莱转债</t>
+          <t>金埔转债</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>57.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>125.86</t>
+          <t>140.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.36年</t>
+          <t>3.13年</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -10508,32 +10508,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>113043</t>
+          <t>110087</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>财通转债</t>
+          <t>天业转债</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>57.83</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>127.57</t>
+          <t>138.39</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.63年</t>
+          <t>2.17年</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -10550,32 +10550,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113605</t>
+          <t>123065</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>大参转债</t>
+          <t>宝莱转债</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>57.00</t>
+          <t>57.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>123.51</t>
+          <t>125.86</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.50年</t>
+          <t>0.36年</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -10592,32 +10592,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>123198</t>
+          <t>113625</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>金埔转债</t>
+          <t>江山转债</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56.81</t>
+          <t>57.53</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>140.24</t>
+          <t>127.08</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.13年</t>
+          <t>1.13年</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -10634,32 +10634,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>113627</t>
+          <t>123109</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>太平转债</t>
+          <t>昌红转债</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>122.83</t>
+          <t>132.04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.22年</t>
+          <t>0.94年</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>127084</t>
+          <t>127061</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>柳工转2</t>
+          <t>美锦转债</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>57.17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>141.95</t>
+          <t>119.10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.93年</t>
+          <t>1.99年</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -10718,32 +10718,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>110085</t>
+          <t>113648</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>通22转债</t>
+          <t>巨星转债</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>56.69</t>
+          <t>57.03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>123.12</t>
+          <t>129.40</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>138.7%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.84年</t>
+          <t>2.01年</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
